--- a/report_forms/014_mineral_expenditure_reporting_form--report_forms.xlsx
+++ b/report_forms/014_mineral_expenditure_reporting_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'aud',_'label':_'australian_dollar'}</t>
+          <t>australian_dollar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'AUD', 'label': 'Australian Dollar'}</t>
+          <t>Australian Dollar</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'usd',_'label':_'us_dollar'}</t>
+          <t>us_dollar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'USD', 'label': 'US Dollar'}</t>
+          <t>US Dollar</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'cad',_'label':_'canadian_dollar'}</t>
+          <t>canadian_dollar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'CAD', 'label': 'Canadian Dollar'}</t>
+          <t>Canadian Dollar</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'draft',_'label':_'draft'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'Draft', 'label': 'Draft'}</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'submitted',_'label':_'submitted'}</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'Submitted', 'label': 'Submitted'}</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'Approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'suspended',_'label':_'suspended'}</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'Suspended', 'label': 'Suspended'}</t>
+          <t>Suspended</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'quarter',_'label':_'quarter'}</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 'Quarter', 'label': 'Quarter'}</t>
+          <t>Quarter</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'semi_annual',_'label':_'semi_annual'}</t>
+          <t>semi_annual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'Semi Annual', 'label': 'Semi Annual'}</t>
+          <t>Semi Annual</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'yearly',_'label':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 'Yearly', 'label': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'mineral_type_a',_'label':_'mineral_type_a'}</t>
+          <t>mineral_type_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 'Mineral Type A', 'label': 'Mineral Type A'}</t>
+          <t>Mineral Type A</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'mineral_type_b',_'label':_'mineral_type_b'}</t>
+          <t>mineral_type_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 'Mineral Type B', 'label': 'Mineral Type B'}</t>
+          <t>Mineral Type B</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'mineral_type_c',_'label':_'mineral_type_c'}</t>
+          <t>mineral_type_c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 'Mineral Type C', 'label': 'Mineral Type C'}</t>
+          <t>Mineral Type C</t>
         </is>
       </c>
     </row>
